--- a/scripts/teacher-imports/account-provisioning/inputs/teacher-accounts-import-5.xlsx
+++ b/scripts/teacher-imports/account-provisioning/inputs/teacher-accounts-import-5.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\teacher-imports\account-provisioning\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C829D8-0A59-427D-95F4-0344BD85EAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44E9F57-9B45-4492-B4AE-0FC939EFBFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="2760" windowWidth="11820" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4380" windowWidth="15315" windowHeight="9045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المعلمين" sheetId="1" r:id="rId1"/>
     <sheet name="تعليمات" sheetId="2" r:id="rId2"/>
+    <sheet name="المعلمين (2)" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
   <si>
     <t>الاسم الكامل</t>
   </si>
@@ -137,13 +138,22 @@
   </si>
   <si>
     <t>m.aljabr@qz.org.sa</t>
+  </si>
+  <si>
+    <t>d-a-athunian@qz.org.sa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ديم عبدالله عبدالكريم الثنيان </t>
+  </si>
+  <si>
+    <t>KF100000101</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -166,8 +176,13 @@
       <sz val="11"/>
       <name val="Tajawal"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tajawal"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -184,8 +199,14 @@
         <fgColor rgb="FF0F766E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -204,11 +225,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,11 +259,62 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Google Sans"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Google Sans"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Tajawal"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -296,16 +377,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAccountsImportTable" displayName="TeacherAccountsImportTable" ref="A1:H3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAccountsImportTable" displayName="TeacherAccountsImportTable" ref="A1:H2">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="الاسم الكامل"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="البريد الإلكتروني"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="كلمة المرور المؤقتة" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="كلمة المرور المؤقتة" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="الرقم الوظيفي"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="معرّف المدرسة" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{EEC87794-B495-480E-A000-1DA2F577E634}" name="الدور" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="معرّف المدرسة" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{EEC87794-B495-480E-A000-1DA2F577E634}" name="الدور" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="حالة الحساب"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="ملاحظات"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{45390FE9-BE15-4913-A5E6-48FC84274126}" name="TeacherAccountsImportTable3" displayName="TeacherAccountsImportTable3" ref="A1:H3">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{63F87721-3E5F-4726-B97E-9DBE159A398D}" name="الاسم الكامل"/>
+    <tableColumn id="2" xr3:uid="{7D0F1571-1855-40BB-9F1B-75C27EB8E96C}" name="البريد الإلكتروني"/>
+    <tableColumn id="3" xr3:uid="{B8B2DBA4-01B3-4CB4-919B-378B2C9F7F1F}" name="كلمة المرور المؤقتة" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{B404983D-7A80-4D6B-A818-B5915B5EC1DA}" name="الرقم الوظيفي"/>
+    <tableColumn id="5" xr3:uid="{F6534A2B-0D34-432E-B969-62F62C6D06F5}" name="معرّف المدرسة" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{718D18CE-09A4-4A21-BC93-9F647C1E2BEE}" name="الدور" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{14CA5326-22F3-4FCF-B322-73B9811227B2}" name="حالة الحساب"/>
+    <tableColumn id="8" xr3:uid="{37703F13-17CE-4FE4-984A-7FAA947B19B3}" name="ملاحظات"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -460,10 +557,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.25" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.25" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
@@ -500,17 +597,17 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.5">
-      <c r="A2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="7">
-        <v>1108035914</v>
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="8">
+        <v>1116361286</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>21</v>
@@ -519,36 +616,13 @@
         <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="16.5">
-      <c r="A3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="7">
-        <v>1092912201</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="G2:G3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="G2" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"نشط,غير نشط"</formula1>
     </dataValidation>
   </dataValidations>
@@ -677,4 +751,105 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA3EAD32-B61B-4745-A901-DD4FA7B7A73F}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="32.25" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" customWidth="1"/>
+    <col min="8" max="8" width="12.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5">
+      <c r="A2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1108035914</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="16.5">
+      <c r="A3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1092912201</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="G2:G3" xr:uid="{5D774559-E241-4AF0-914D-94DBC90DA219}">
+      <formula1>"نشط,غير نشط"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>